--- a/Codes/Trial 1/Trial1_LSTM_Followers_Results.xlsx
+++ b/Codes/Trial 1/Trial1_LSTM_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         <v>2020</v>
       </c>
       <c r="C2" t="n">
-        <v>2.24</v>
+        <v>4.96</v>
       </c>
       <c r="D2" t="n">
-        <v>1.221826434135437</v>
+        <v>1.597809076309204</v>
       </c>
       <c r="E2" t="n">
-        <v>1.018173565864563</v>
+        <v>3.362190923690796</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2021</v>
       </c>
       <c r="C3" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="D3" t="n">
-        <v>1.694777131080627</v>
+        <v>1.115464210510254</v>
       </c>
       <c r="E3" t="n">
-        <v>1.545222868919372</v>
+        <v>1.364535789489746</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2022</v>
       </c>
       <c r="C4" t="n">
-        <v>4.56</v>
+        <v>4.01</v>
       </c>
       <c r="D4" t="n">
-        <v>2.570651054382324</v>
+        <v>1.218867540359497</v>
       </c>
       <c r="E4" t="n">
-        <v>1.989348945617676</v>
+        <v>2.791132459640503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>5.9</v>
+        <v>4.040000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>3.107161045074463</v>
+        <v>1.685646414756775</v>
       </c>
       <c r="E5" t="n">
-        <v>2.792838954925537</v>
+        <v>2.354353585243226</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2024</v>
       </c>
       <c r="C6" t="n">
-        <v>4.96</v>
+        <v>3.87</v>
       </c>
       <c r="D6" t="n">
-        <v>3.404332637786865</v>
+        <v>1.917227745056152</v>
       </c>
       <c r="E6" t="n">
-        <v>1.555667362213135</v>
+        <v>1.952772254943847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2020</v>
       </c>
       <c r="C7" t="n">
-        <v>2.48</v>
+        <v>3.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.182348251342773</v>
+        <v>1.558189511299133</v>
       </c>
       <c r="E7" t="n">
-        <v>1.297651748657227</v>
+        <v>2.201810488700866</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2021</v>
       </c>
       <c r="C8" t="n">
-        <v>4.01</v>
+        <v>1.42</v>
       </c>
       <c r="D8" t="n">
-        <v>1.933359742164612</v>
+        <v>1.510139465332031</v>
       </c>
       <c r="E8" t="n">
-        <v>2.076640257835388</v>
+        <v>0.09013946533203132</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2022</v>
       </c>
       <c r="C9" t="n">
-        <v>4.040000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="D9" t="n">
-        <v>2.765187501907349</v>
+        <v>0.9936011433601379</v>
       </c>
       <c r="E9" t="n">
-        <v>1.274812498092652</v>
+        <v>0.7563988566398621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>3.87</v>
+        <v>4.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.349680662155151</v>
+        <v>1.35032331943512</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5203193378448483</v>
+        <v>2.74967668056488</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2024</v>
       </c>
       <c r="C11" t="n">
-        <v>3.76</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>4.86469554901123</v>
+        <v>2.218579053878784</v>
       </c>
       <c r="E11" t="n">
-        <v>1.104695549011231</v>
+        <v>4.171420946121217</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2020</v>
       </c>
       <c r="C12" t="n">
-        <v>1.42</v>
+        <v>8.919999999999998</v>
       </c>
       <c r="D12" t="n">
-        <v>1.115643382072449</v>
+        <v>1.232279777526855</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3043566179275512</v>
+        <v>7.687720222473143</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2021</v>
       </c>
       <c r="C13" t="n">
-        <v>1.75</v>
+        <v>2.92</v>
       </c>
       <c r="D13" t="n">
-        <v>2.151714563369751</v>
+        <v>1.129035592079163</v>
       </c>
       <c r="E13" t="n">
-        <v>0.401714563369751</v>
+        <v>1.790964407920837</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2022</v>
       </c>
       <c r="C14" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="D14" t="n">
-        <v>3.295653104782104</v>
+        <v>1.100886225700378</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8043468952178952</v>
+        <v>2.149113774299622</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         <v>2023</v>
       </c>
       <c r="C15" t="n">
-        <v>6.390000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="D15" t="n">
-        <v>3.731389760971069</v>
+        <v>1.472800374031067</v>
       </c>
       <c r="E15" t="n">
-        <v>2.658610239028932</v>
+        <v>2.827199625968933</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>8.919999999999998</v>
+        <v>7.390000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9896240234375</v>
+        <v>3.147064685821533</v>
       </c>
       <c r="E16" t="n">
-        <v>4.930375976562498</v>
+        <v>4.242935314178467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         <v>2020</v>
       </c>
       <c r="C17" t="n">
-        <v>2.92</v>
+        <v>6.200000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09378457069397</v>
+        <v>1.745681881904602</v>
       </c>
       <c r="E17" t="n">
-        <v>1.82621542930603</v>
+        <v>4.454318118095399</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>2021</v>
       </c>
       <c r="C18" t="n">
-        <v>3.25</v>
+        <v>1.84</v>
       </c>
       <c r="D18" t="n">
-        <v>1.788410663604736</v>
+        <v>1.048006057739258</v>
       </c>
       <c r="E18" t="n">
-        <v>1.461589336395264</v>
+        <v>0.7919939422607423</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         <v>2022</v>
       </c>
       <c r="C19" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.532774448394775</v>
+        <v>1.299087285995483</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7672255516052244</v>
+        <v>1.800912714004517</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>7.390000000000001</v>
+        <v>3.51</v>
       </c>
       <c r="D20" t="n">
-        <v>3.916485548019409</v>
+        <v>1.812640428543091</v>
       </c>
       <c r="E20" t="n">
-        <v>3.473514451980591</v>
+        <v>1.697359571456909</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         <v>2024</v>
       </c>
       <c r="C21" t="n">
-        <v>6.200000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3.56496262550354</v>
+        <v>2.328024387359619</v>
       </c>
       <c r="E21" t="n">
-        <v>2.635037374496461</v>
+        <v>3.171975612640381</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         <v>2020</v>
       </c>
       <c r="C22" t="n">
-        <v>1.84</v>
+        <v>6.920000000000002</v>
       </c>
       <c r="D22" t="n">
-        <v>1.171580672264099</v>
+        <v>1.277857899665833</v>
       </c>
       <c r="E22" t="n">
-        <v>0.668419327735901</v>
+        <v>5.642142100334169</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         <v>2021</v>
       </c>
       <c r="C23" t="n">
-        <v>3.1</v>
+        <v>5.459999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>2.318717956542969</v>
+        <v>1.289274334907532</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7812820434570313</v>
+        <v>4.170725665092467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -998,13 +998,13 @@
         <v>2022</v>
       </c>
       <c r="C24" t="n">
-        <v>3.51</v>
+        <v>9.320000000000002</v>
       </c>
       <c r="D24" t="n">
-        <v>2.901862859725952</v>
+        <v>1.227796316146851</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6081371402740481</v>
+        <v>8.092203683853151</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1022,13 +1022,13 @@
         <v>2023</v>
       </c>
       <c r="C25" t="n">
-        <v>5.5</v>
+        <v>15.91000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>3.130933523178101</v>
+        <v>2.249017715454102</v>
       </c>
       <c r="E25" t="n">
-        <v>2.369066476821899</v>
+        <v>13.6609822845459</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         <v>2024</v>
       </c>
       <c r="C26" t="n">
-        <v>6.920000000000002</v>
+        <v>19.77</v>
       </c>
       <c r="D26" t="n">
-        <v>3.325888872146606</v>
+        <v>3.107937335968018</v>
       </c>
       <c r="E26" t="n">
-        <v>3.594111127853395</v>
+        <v>16.66206266403198</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1070,13 +1070,13 @@
         <v>2020</v>
       </c>
       <c r="C27" t="n">
-        <v>5.459999999999999</v>
+        <v>15.39</v>
       </c>
       <c r="D27" t="n">
-        <v>1.127225756645203</v>
+        <v>1.783865094184875</v>
       </c>
       <c r="E27" t="n">
-        <v>4.332774243354796</v>
+        <v>13.60613490581513</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1094,13 +1094,13 @@
         <v>2021</v>
       </c>
       <c r="C28" t="n">
-        <v>9.320000000000002</v>
+        <v>3.14</v>
       </c>
       <c r="D28" t="n">
-        <v>2.543320417404175</v>
+        <v>1.185817241668701</v>
       </c>
       <c r="E28" t="n">
-        <v>6.776679582595827</v>
+        <v>1.954182758331299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1118,13 +1118,13 @@
         <v>2022</v>
       </c>
       <c r="C29" t="n">
-        <v>15.91000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="D29" t="n">
-        <v>3.398018598556519</v>
+        <v>1.141225218772888</v>
       </c>
       <c r="E29" t="n">
-        <v>12.51198140144349</v>
+        <v>2.798774781227111</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>19.77</v>
+        <v>7.38</v>
       </c>
       <c r="D30" t="n">
-        <v>3.357434034347534</v>
+        <v>1.455854058265686</v>
       </c>
       <c r="E30" t="n">
-        <v>16.41256596565246</v>
+        <v>5.924145941734314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1166,13 +1166,13 @@
         <v>2024</v>
       </c>
       <c r="C31" t="n">
-        <v>15.39</v>
+        <v>10.48</v>
       </c>
       <c r="D31" t="n">
-        <v>3.5596923828125</v>
+        <v>1.974953532218933</v>
       </c>
       <c r="E31" t="n">
-        <v>11.8303076171875</v>
+        <v>8.505046467781066</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1190,13 +1190,13 @@
         <v>2020</v>
       </c>
       <c r="C32" t="n">
-        <v>3.14</v>
+        <v>8.520000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>1.208521842956543</v>
+        <v>1.575172305107117</v>
       </c>
       <c r="E32" t="n">
-        <v>1.931478157043457</v>
+        <v>6.944827694892885</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         <v>2021</v>
       </c>
       <c r="C33" t="n">
-        <v>3.94</v>
+        <v>2.13</v>
       </c>
       <c r="D33" t="n">
-        <v>1.587652444839478</v>
+        <v>0.8213775753974915</v>
       </c>
       <c r="E33" t="n">
-        <v>2.352347555160522</v>
+        <v>1.308622424602508</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1238,13 +1238,13 @@
         <v>2022</v>
       </c>
       <c r="C34" t="n">
-        <v>7.38</v>
+        <v>4.609999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>2.610669136047363</v>
+        <v>1.425871133804321</v>
       </c>
       <c r="E34" t="n">
-        <v>4.769330863952637</v>
+        <v>3.184128866195678</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         <v>2023</v>
       </c>
       <c r="C35" t="n">
-        <v>10.48</v>
+        <v>6.159999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>3.537661552429199</v>
+        <v>1.675175309181213</v>
       </c>
       <c r="E35" t="n">
-        <v>6.942338447570799</v>
+        <v>4.484824690818786</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1286,13 +1286,13 @@
         <v>2024</v>
       </c>
       <c r="C36" t="n">
-        <v>8.520000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="D36" t="n">
-        <v>3.058274030685425</v>
+        <v>3.469514131546021</v>
       </c>
       <c r="E36" t="n">
-        <v>5.461725969314577</v>
+        <v>4.93048586845398</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1310,13 +1310,13 @@
         <v>2020</v>
       </c>
       <c r="C37" t="n">
-        <v>2.13</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>1.215888738632202</v>
+        <v>1.453713178634644</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9141112613677977</v>
+        <v>6.196286821365356</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         <v>2021</v>
       </c>
       <c r="C38" t="n">
-        <v>4.609999999999999</v>
+        <v>6.590000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>1.93931245803833</v>
+        <v>0.9180468320846558</v>
       </c>
       <c r="E38" t="n">
-        <v>2.670687541961669</v>
+        <v>5.671953167915345</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         <v>2022</v>
       </c>
       <c r="C39" t="n">
-        <v>6.159999999999999</v>
+        <v>11.56</v>
       </c>
       <c r="D39" t="n">
-        <v>3.50139331817627</v>
+        <v>1.600756525993347</v>
       </c>
       <c r="E39" t="n">
-        <v>2.65860668182373</v>
+        <v>9.959243474006657</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1382,13 +1382,13 @@
         <v>2023</v>
       </c>
       <c r="C40" t="n">
-        <v>8.4</v>
+        <v>16.82</v>
       </c>
       <c r="D40" t="n">
-        <v>3.319653511047363</v>
+        <v>1.665480375289917</v>
       </c>
       <c r="E40" t="n">
-        <v>5.080346488952637</v>
+        <v>15.15451962471008</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>2024</v>
       </c>
       <c r="C41" t="n">
-        <v>7.649999999999999</v>
+        <v>24.15</v>
       </c>
       <c r="D41" t="n">
-        <v>3.561213970184326</v>
+        <v>1.823252439498901</v>
       </c>
       <c r="E41" t="n">
-        <v>4.088786029815673</v>
+        <v>22.3267475605011</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         <v>2020</v>
       </c>
       <c r="C42" t="n">
-        <v>6.590000000000001</v>
+        <v>28.37</v>
       </c>
       <c r="D42" t="n">
-        <v>1.478628158569336</v>
+        <v>1.327550530433655</v>
       </c>
       <c r="E42" t="n">
-        <v>5.111371841430665</v>
+        <v>27.04244946956635</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1454,13 +1454,13 @@
         <v>2021</v>
       </c>
       <c r="C43" t="n">
-        <v>11.56</v>
+        <v>2.23</v>
       </c>
       <c r="D43" t="n">
-        <v>2.124874830245972</v>
+        <v>1.126422643661499</v>
       </c>
       <c r="E43" t="n">
-        <v>9.435125169754032</v>
+        <v>1.103577356338501</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1478,13 +1478,13 @@
         <v>2022</v>
       </c>
       <c r="C44" t="n">
-        <v>16.82</v>
+        <v>2.5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.934137582778931</v>
+        <v>1.500583291053772</v>
       </c>
       <c r="E44" t="n">
-        <v>13.88586241722107</v>
+        <v>0.9994167089462285</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>24.15</v>
+        <v>2.940000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>3.278780937194824</v>
+        <v>1.467936754226685</v>
       </c>
       <c r="E45" t="n">
-        <v>20.87121906280518</v>
+        <v>1.472063245773316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1526,13 +1526,13 @@
         <v>2024</v>
       </c>
       <c r="C46" t="n">
-        <v>28.37</v>
+        <v>15.94999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>3.519924879074097</v>
+        <v>2.290517807006836</v>
       </c>
       <c r="E46" t="n">
-        <v>24.8500751209259</v>
+        <v>13.65948219299316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1550,13 +1550,13 @@
         <v>2020</v>
       </c>
       <c r="C47" t="n">
-        <v>2.23</v>
+        <v>39.77999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>1.664406180381775</v>
+        <v>2.332546234130859</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5655938196182251</v>
+        <v>37.44745376586913</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         <v>2021</v>
       </c>
       <c r="C48" t="n">
-        <v>2.5</v>
+        <v>6.400000000000002</v>
       </c>
       <c r="D48" t="n">
-        <v>2.150293350219727</v>
+        <v>1.145293235778809</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3497066497802739</v>
+        <v>5.254706764221194</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1598,13 +1598,13 @@
         <v>2022</v>
       </c>
       <c r="C49" t="n">
-        <v>2.940000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="D49" t="n">
-        <v>3.59818172454834</v>
+        <v>1.165729403495789</v>
       </c>
       <c r="E49" t="n">
-        <v>0.658181724548339</v>
+        <v>8.874270596504209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1622,13 +1622,13 @@
         <v>2023</v>
       </c>
       <c r="C50" t="n">
-        <v>15.94999999999999</v>
+        <v>12.39</v>
       </c>
       <c r="D50" t="n">
-        <v>5.173340797424316</v>
+        <v>1.912305593490601</v>
       </c>
       <c r="E50" t="n">
-        <v>10.77665920257568</v>
+        <v>10.4776944065094</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1646,13 +1646,13 @@
         <v>2024</v>
       </c>
       <c r="C51" t="n">
-        <v>39.77999999999999</v>
+        <v>19.21</v>
       </c>
       <c r="D51" t="n">
-        <v>5.11681079864502</v>
+        <v>2.53066086769104</v>
       </c>
       <c r="E51" t="n">
-        <v>34.66318920135497</v>
+        <v>16.67933913230896</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         <v>2020</v>
       </c>
       <c r="C52" t="n">
-        <v>6.400000000000002</v>
+        <v>21.05999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>1.166920185089111</v>
+        <v>1.447551131248474</v>
       </c>
       <c r="E52" t="n">
-        <v>5.233079814910891</v>
+        <v>19.61244886875152</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1694,13 +1694,13 @@
         <v>2021</v>
       </c>
       <c r="C53" t="n">
-        <v>10.04</v>
+        <v>2.19</v>
       </c>
       <c r="D53" t="n">
-        <v>1.775424122810364</v>
+        <v>1.308429479598999</v>
       </c>
       <c r="E53" t="n">
-        <v>8.264575877189634</v>
+        <v>0.8815705204010009</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>2022</v>
       </c>
       <c r="C54" t="n">
-        <v>12.39</v>
+        <v>2.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2.863969802856445</v>
+        <v>1.714332580566406</v>
       </c>
       <c r="E54" t="n">
-        <v>9.526030197143553</v>
+        <v>0.7856674194335942</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         <v>2023</v>
       </c>
       <c r="C55" t="n">
-        <v>19.21</v>
+        <v>2.91</v>
       </c>
       <c r="D55" t="n">
-        <v>3.09763765335083</v>
+        <v>1.737463355064392</v>
       </c>
       <c r="E55" t="n">
-        <v>16.11236234664917</v>
+        <v>1.172536644935608</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1766,13 +1766,13 @@
         <v>2024</v>
       </c>
       <c r="C56" t="n">
-        <v>21.05999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="D56" t="n">
-        <v>3.227551937103271</v>
+        <v>2.327763080596924</v>
       </c>
       <c r="E56" t="n">
-        <v>17.83244806289672</v>
+        <v>1.532236919403076</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1790,13 +1790,13 @@
         <v>2020</v>
       </c>
       <c r="C57" t="n">
-        <v>2.19</v>
+        <v>3.34</v>
       </c>
       <c r="D57" t="n">
-        <v>1.231709837913513</v>
+        <v>1.564014911651611</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9582901620864868</v>
+        <v>1.775985088348389</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1814,13 +1814,13 @@
         <v>2021</v>
       </c>
       <c r="C58" t="n">
-        <v>2.5</v>
+        <v>4.12</v>
       </c>
       <c r="D58" t="n">
-        <v>1.639574527740479</v>
+        <v>1.073570251464844</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8604254722595219</v>
+        <v>3.046429748535156</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1838,13 +1838,13 @@
         <v>2022</v>
       </c>
       <c r="C59" t="n">
-        <v>2.91</v>
+        <v>4.13</v>
       </c>
       <c r="D59" t="n">
-        <v>2.706092119216919</v>
+        <v>1.234624028205872</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2039078807830812</v>
+        <v>2.895375971794128</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1862,13 +1862,13 @@
         <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>3.86</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>3.01716160774231</v>
+        <v>1.606931567192078</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8428383922576903</v>
+        <v>4.393068432807922</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1886,13 +1886,13 @@
         <v>2024</v>
       </c>
       <c r="C61" t="n">
-        <v>3.34</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>3.214426279067993</v>
+        <v>2.003883123397827</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1255737209320067</v>
+        <v>7.856116876602172</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -1910,111 +1910,15 @@
         <v>2020</v>
       </c>
       <c r="C62" t="n">
-        <v>4.12</v>
+        <v>6.980000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>1.188090324401855</v>
+        <v>1.509408593177795</v>
       </c>
       <c r="E62" t="n">
-        <v>2.931909675598145</v>
+        <v>5.470591406822206</v>
       </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.865338206291199</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2.264661793708801</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C64" t="n">
-        <v>6</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.942912340164185</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3.057087659835815</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C65" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="D65" t="n">
-        <v>3.32689380645752</v>
-      </c>
-      <c r="E65" t="n">
-        <v>6.53310619354248</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C66" t="n">
-        <v>6.980000000000001</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3.450321912765503</v>
-      </c>
-      <c r="E66" t="n">
-        <v>3.529678087234498</v>
-      </c>
-      <c r="F66" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
